--- a/output/pdf_financials_xlsx/MCM.A.xlsx
+++ b/output/pdf_financials_xlsx/MCM.A.xlsx
@@ -5309,7 +5309,7 @@
         <v>-0.7095359999999999</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1.43876</v>
+        <v>-1.43876</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.592902</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="N124" s="5" t="n">
-        <v>1.43876</v>
+        <v>-1.43876</v>
       </c>
       <c r="O124" s="5" t="n">
         <v>-0.592902</v>

--- a/output/pdf_financials_xlsx/MCM.A.xlsx
+++ b/output/pdf_financials_xlsx/MCM.A.xlsx
@@ -2090,43 +2090,43 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.007488</v>
+        <v>0.068407</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.089201</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.080593</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.178206</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.252536</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001361</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.443962</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.253233</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.17216</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.393582</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.123126</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.07614700000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.100939</v>
       </c>
     </row>
     <row r="35">
@@ -2188,43 +2188,43 @@
         <v>0.21496</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.533444</v>
+        <v>2.594363</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.917393</v>
+        <v>2.006594</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.564647</v>
+        <v>0.64524</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.929334</v>
+        <v>1.10754</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.364916</v>
+        <v>1.617452</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3.296218</v>
+        <v>3.297579</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.26802</v>
+        <v>3.711982</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.39636</v>
+        <v>2.649593</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>5.707714</v>
+        <v>5.879874</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>5.83081</v>
+        <v>6.224392</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6.907271</v>
+        <v>7.030397</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.783625000000001</v>
+        <v>8.859772</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>5.144194</v>
+        <v>12.245133</v>
       </c>
     </row>
     <row r="37">
@@ -2776,43 +2776,43 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.101919</v>
+        <v>0.041</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.149791</v>
+        <v>0.06059</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.085593</v>
+        <v>0.005</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.178206</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.102536</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.293962</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.143233</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.128135</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.393582</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.20429</v>
+        <v>0.081164</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.137224</v>
+        <v>0.061077</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.4204</v>
+        <v>0.319461</v>
       </c>
     </row>
     <row r="49">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCM.A.xlsx
+++ b/output/pdf_financials_xlsx/MCM.A.xlsx
@@ -6017,46 +6017,46 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.736467</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-4.768721</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-2.931377</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.961417</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.71025</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-1.194231</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-3.830472</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-1.683285</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.549488</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.483628</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-5.601119</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-1.827578</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.566984</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-0.073842</v>
       </c>
     </row>
     <row r="115">
@@ -6066,46 +6066,46 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.607982</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.329001</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>3.175809</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.83962</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.163292</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.441999</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>3.130328</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.746922</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.777157</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.345488</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>5.087519</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.525733</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.759646</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>7.521376</v>
       </c>
     </row>
     <row r="116">
@@ -13448,7 +13448,11 @@
           <t>Purchase of marketable securities (Note 3, 6, 9)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13526,7 +13530,11 @@
           <t>Proceeds on sale of marketable securities (Note 3, 6, 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -15318,7 +15326,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16428,7 +16440,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>-0.736467</v>
       </c>
@@ -16494,7 +16510,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.607982</v>
       </c>
